--- a/bill of materials/Bil of materials.xlsx
+++ b/bill of materials/Bil of materials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeroe\OneDrive\Bureaublad\Shool\Syn Project\Xander\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2468BBE-5F95-4E2D-9A83-544D46519C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3AB596D-5495-4AF5-BAD9-3807419569DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{0426FEB5-BFCA-44BB-8F5E-4FD81A1ECDD7}"/>
   </bookViews>
@@ -1113,11 +1113,11 @@
         <v>3.5</v>
       </c>
       <c r="G18" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" s="6">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>57</v>
@@ -1206,7 +1206,7 @@
       <c r="G22" s="9"/>
       <c r="H22" s="3">
         <f>SUM(H3:H21)</f>
-        <v>73.06</v>
+        <v>69.56</v>
       </c>
     </row>
   </sheetData>
